--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487475_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487475_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. GUERRA TRUJILLO</t>
+          <t>A. HARRIS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.2592</v>
+        <v>7.6891</v>
       </c>
       <c r="E2" t="n">
-        <v>7.778</v>
+        <v>8.7887</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4812</v>
+        <v>-1.0995</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7012</v>
+        <v>2.2914</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5084</v>
+        <v>-0.1944</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1928</v>
+        <v>2.4857</v>
       </c>
       <c r="J2" t="n">
-        <v>8.160600000000001</v>
+        <v>5.909</v>
       </c>
       <c r="K2" t="n">
-        <v>5.5239</v>
+        <v>1.5701</v>
       </c>
       <c r="L2" t="n">
-        <v>2.6366</v>
+        <v>4.3389</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.4594</v>
+        <v>-3.6176</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0156</v>
+        <v>-1.7645</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.4438</v>
+        <v>-1.8532</v>
       </c>
       <c r="P2" t="n">
+        <v>0.5875</v>
+      </c>
+      <c r="Q2" t="n">
         <v>-1.9585</v>
       </c>
-      <c r="Q2" t="n">
-        <v>-3.917</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.9585</v>
+        <v>2.546</v>
       </c>
       <c r="S2" t="n">
-        <v>1.5326</v>
+        <v>0.3344</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5505</v>
+        <v>0.3623</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9821</v>
+        <v>-0.0279</v>
       </c>
       <c r="V2" t="n">
-        <v>2.9839</v>
+        <v>4.4759</v>
       </c>
       <c r="W2" t="n">
-        <v>2.9839</v>
+        <v>4.4759</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. HARRIS</t>
+          <t>D. GUERRA TRUJILLO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.4295</v>
+        <v>7.2842</v>
       </c>
       <c r="E3" t="n">
-        <v>7.6894</v>
+        <v>7.4445</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2599</v>
+        <v>-0.1603</v>
       </c>
       <c r="G3" t="n">
-        <v>2.2914</v>
+        <v>5.7012</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1944</v>
+        <v>4.5084</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4857</v>
+        <v>1.1928</v>
       </c>
       <c r="J3" t="n">
-        <v>5.909</v>
+        <v>8.160600000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5701</v>
+        <v>5.5239</v>
       </c>
       <c r="L3" t="n">
-        <v>4.3389</v>
+        <v>2.6366</v>
       </c>
       <c r="M3" t="n">
-        <v>-3.6176</v>
+        <v>-2.4594</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.7645</v>
+        <v>-1.0156</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.8532</v>
+        <v>-1.4438</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5875</v>
+        <v>-1.9585</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R3" t="n">
-        <v>2.546</v>
+        <v>1.9585</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9253</v>
+        <v>0.5576</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7369</v>
+        <v>0.217</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1883</v>
+        <v>0.3405</v>
       </c>
       <c r="V3" t="n">
-        <v>4.4759</v>
+        <v>2.9839</v>
       </c>
       <c r="W3" t="n">
-        <v>4.4759</v>
+        <v>2.9839</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3229</v>
+        <v>4.2103</v>
       </c>
       <c r="E4" t="n">
-        <v>3.34</v>
+        <v>3.2541</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9829</v>
+        <v>0.9562</v>
       </c>
       <c r="G4" t="n">
         <v>2.9754</v>
@@ -766,13 +766,13 @@
         <v>1.3709</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0722</v>
+        <v>-0.0404</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0882</v>
+        <v>0.0023</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.016</v>
+        <v>-0.0428</v>
       </c>
       <c r="V4" t="n">
         <v>0.8837</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BARRIO</t>
+          <t>R. VARELA BARRAL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0542</v>
+        <v>0.1771</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.0245</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1169</v>
+        <v>0.1526</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3335</v>
+        <v>0.3581</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1514</v>
+        <v>0.5802</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1821</v>
+        <v>-0.2221</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1221</v>
+        <v>0.7549</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08169999999999999</v>
+        <v>0.7145</v>
       </c>
       <c r="L5" t="n">
         <v>0.0404</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2114</v>
+        <v>-0.3969</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0698</v>
+        <v>-0.1344</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1416</v>
+        <v>-0.2625</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>0.9792</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1123</v>
+        <v>-0.181</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0594</v>
+        <v>0.2488</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0529</v>
+        <v>-0.4298</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. LOPEZ MOURE</t>
+          <t>J. RODRIGUEZ BARRIO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1151</v>
+        <v>0.0481</v>
       </c>
       <c r="E6" t="n">
-        <v>1.0798</v>
+        <v>0.165</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1949</v>
+        <v>-0.1169</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.1202</v>
+        <v>0.3335</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6308</v>
+        <v>0.1514</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4894</v>
+        <v>0.1821</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2245</v>
+        <v>0.1221</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8608</v>
+        <v>0.08169999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3637</v>
+        <v>0.0404</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.3447</v>
+        <v>0.2114</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4916</v>
+        <v>0.0698</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.8532</v>
+        <v>0.1416</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5875</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.546</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1.4176</v>
+        <v>-0.01</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8138</v>
+        <v>0.0429</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3962</v>
+        <v>-0.0529</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. VARELA BARRAL</t>
+          <t>M. ALVAREZ HERNAN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2055</v>
+        <v>-0.4039</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3849</v>
+        <v>1.2867</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1793</v>
+        <v>-1.6906</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3581</v>
+        <v>-1.5042</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5802</v>
+        <v>0.4212</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2221</v>
+        <v>-1.9255</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7549</v>
+        <v>1.5009</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7145</v>
+        <v>1.7097</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0404</v>
+        <v>-0.2087</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3969</v>
+        <v>-3.0052</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1344</v>
+        <v>-1.2884</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2625</v>
+        <v>-1.7167</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9792</v>
+        <v>1.9585</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5636</v>
+        <v>0.7674</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1606</v>
+        <v>0.2523</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.403</v>
+        <v>0.5151</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. ALVAREZ HERNAN</t>
+          <t>D. LOPEZ MOURE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.9159</v>
+        <v>-0.7685</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8015</v>
+        <v>0.1323</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7174</v>
+        <v>-0.9009</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5042</v>
+        <v>-2.1202</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4212</v>
+        <v>-0.6308</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.9255</v>
+        <v>-1.4894</v>
       </c>
       <c r="J8" t="n">
-        <v>1.5009</v>
+        <v>1.2245</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7097</v>
+        <v>0.8608</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2087</v>
+        <v>0.3637</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.0052</v>
+        <v>-3.3447</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2884</v>
+        <v>-1.4916</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.7167</v>
+        <v>-1.8532</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.5875</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.9585</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9585</v>
+        <v>2.546</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2554</v>
+        <v>0.7641</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2329</v>
+        <v>0.8663</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4883</v>
+        <v>-0.1022</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.159</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.7414</v>
+        <v>-6.3659</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.4735</v>
+        <v>-5.3118</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2679</v>
+        <v>-1.0541</v>
       </c>
       <c r="G9" t="n">
         <v>-4.8949</v>
@@ -1156,13 +1156,13 @@
         <v>1.3709</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2797</v>
+        <v>0.0959</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0047</v>
+        <v>0.1664</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2844</v>
+        <v>-0.0706</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,22 +1189,22 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>10.9795</v>
+        <v>11.8705</v>
       </c>
       <c r="E10" t="n">
-        <v>14.893</v>
+        <v>15.784</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.9136</v>
+        <v>-3.9135</v>
       </c>
       <c r="G10" t="n">
-        <v>3.140299999999998</v>
+        <v>3.1403</v>
       </c>
       <c r="H10" t="n">
         <v>6.4734</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.333299999999999</v>
+        <v>-3.3333</v>
       </c>
       <c r="J10" t="n">
         <v>18.8119</v>
@@ -1234,16 +1234,16 @@
         <v>12.73</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3969</v>
+        <v>2.288</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2674</v>
+        <v>2.1583</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1296</v>
+        <v>0.1294</v>
       </c>
       <c r="V10" t="n">
-        <v>8.401000000000002</v>
+        <v>8.401</v>
       </c>
       <c r="W10" t="n">
         <v>9.502600000000001</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9811</v>
+        <v>1.9565</v>
       </c>
       <c r="E11" t="n">
-        <v>1.315</v>
+        <v>2.3384</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3339</v>
+        <v>-0.3818</v>
       </c>
       <c r="G11" t="n">
         <v>0.451</v>
@@ -1312,13 +1312,13 @@
         <v>2.546</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3407</v>
+        <v>-0.3652</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2892</v>
+        <v>-0.2658</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0515</v>
+        <v>-0.0994</v>
       </c>
       <c r="V11" t="n">
         <v>1.2832</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ BUCETA</t>
+          <t>R. SANTORUM OTERO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.89</v>
+        <v>0.7285</v>
       </c>
       <c r="E12" t="n">
-        <v>3.6247</v>
+        <v>1.3801</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.7347</v>
+        <v>-0.6516</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0149</v>
+        <v>-0.2921</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.031</v>
+        <v>-0.9187</v>
       </c>
       <c r="I12" t="n">
-        <v>0.046</v>
+        <v>0.6266</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7732</v>
+        <v>1.3954</v>
       </c>
       <c r="K12" t="n">
-        <v>1.8032</v>
+        <v>0.1021</v>
       </c>
       <c r="L12" t="n">
-        <v>0.97</v>
+        <v>1.2933</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.7582</v>
+        <v>-1.6874</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.8342</v>
+        <v>-1.0208</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.924</v>
+        <v>-0.6667</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5875</v>
+        <v>1.1751</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5668</v>
+        <v>1.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>2.0458</v>
+        <v>-0.1545</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1637</v>
+        <v>-0.0153</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1179</v>
+        <v>-0.1392</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.7583</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.4254</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R. SANTORUM OTERO</t>
+          <t>M. BELLO CASTRO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4436</v>
+        <v>0.4156</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1754</v>
+        <v>-0.3512</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7318</v>
+        <v>0.7668</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2921</v>
+        <v>1.3707</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9187</v>
+        <v>0.1783</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6266</v>
+        <v>1.1924</v>
       </c>
       <c r="J13" t="n">
-        <v>1.3954</v>
+        <v>0.6875</v>
       </c>
       <c r="K13" t="n">
-        <v>0.1021</v>
+        <v>0.0408</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2933</v>
+        <v>0.6466</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.6874</v>
+        <v>0.6833</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.0208</v>
+        <v>0.1375</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.6667</v>
+        <v>0.5458</v>
       </c>
       <c r="P13" t="n">
-        <v>1.1751</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4394</v>
+        <v>-0.1717</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.22</v>
+        <v>-0.0594</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2194</v>
+        <v>-0.1123</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. BELLO CASTRO</t>
+          <t>D. REY MARIÑO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,58 +1501,58 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2792</v>
+        <v>-0.2117</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3512</v>
+        <v>0.0239</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6303</v>
+        <v>-0.2356</v>
       </c>
       <c r="G14" t="n">
-        <v>1.3707</v>
+        <v>-0.4356</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1783</v>
+        <v>-0.476</v>
       </c>
       <c r="I14" t="n">
-        <v>1.1924</v>
+        <v>0.0404</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6875</v>
+        <v>0.0404</v>
       </c>
       <c r="K14" t="n">
-        <v>0.0408</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6466</v>
+        <v>0.0404</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6833</v>
+        <v>-0.476</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1375</v>
+        <v>-0.476</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5458</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7834</v>
+        <v>0.1958</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0.1958</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3082</v>
+        <v>0.0281</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0594</v>
+        <v>-0.0165</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2488</v>
+        <v>0.0446</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. REY MARIÑO</t>
+          <t>J. RODRIGUEZ BUCETA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.3407</v>
+        <v>-0.4773</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0784</v>
+        <v>1.9874</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2623</v>
+        <v>-2.4646</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4356</v>
+        <v>0.0149</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.476</v>
+        <v>-0.031</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0404</v>
+        <v>0.046</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0404</v>
+        <v>2.7732</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1.8032</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0404</v>
+        <v>0.97</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.476</v>
+        <v>-2.7582</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.476</v>
+        <v>-1.8342</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>-0.924</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1958</v>
+        <v>0.5875</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R15" t="n">
-        <v>0.1958</v>
+        <v>1.5668</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.101</v>
+        <v>0.6786</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1188</v>
+        <v>0.5264</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0178</v>
+        <v>0.1522</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.7583</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.4254</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.8519</v>
+        <v>-1.5938</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.8003</v>
+        <v>-0.5957</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0516</v>
+        <v>-0.9981</v>
       </c>
       <c r="G16" t="n">
         <v>-1.0668</v>
@@ -1702,13 +1702,13 @@
         <v>1.5668</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5937</v>
+        <v>-0.3355</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4752</v>
+        <v>-0.2705</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1184</v>
+        <v>-0.065</v>
       </c>
       <c r="V16" t="n">
         <v>-1.7583</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. GIL RODRIGUEZ</t>
+          <t>O. CASTAÑO RUBIANES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.0008</v>
+        <v>-2.0206</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3063</v>
+        <v>0.782</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.3071</v>
+        <v>-2.8026</v>
       </c>
       <c r="G17" t="n">
-        <v>0.319</v>
+        <v>0.8655</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3753</v>
+        <v>1.168</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0564</v>
+        <v>-0.3026</v>
       </c>
       <c r="J17" t="n">
-        <v>3.6053</v>
+        <v>4.0279</v>
       </c>
       <c r="K17" t="n">
-        <v>3.6168</v>
+        <v>3.1387</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0115</v>
+        <v>0.8891</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.2864</v>
+        <v>-3.1624</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.2415</v>
+        <v>-1.9707</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0449</v>
+        <v>-1.1917</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.1958</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.9377</v>
       </c>
       <c r="R17" t="n">
-        <v>2.7419</v>
+        <v>2.3502</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2427</v>
+        <v>-0.5402</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6387</v>
+        <v>-0.2506</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.396</v>
+        <v>-0.2897</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.3666</v>
+        <v>-1.7583</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.0576</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.3666</v>
+        <v>-1.7007</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O. CASTAÑO RUBIANES</t>
+          <t>M. GIL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2105</v>
+        <v>-2.1862</v>
       </c>
       <c r="E18" t="n">
-        <v>0.782</v>
+        <v>0.7946</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.9925</v>
+        <v>-2.9808</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8655</v>
+        <v>0.319</v>
       </c>
       <c r="H18" t="n">
-        <v>1.168</v>
+        <v>1.3753</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3026</v>
+        <v>-1.0564</v>
       </c>
       <c r="J18" t="n">
-        <v>4.0279</v>
+        <v>3.6053</v>
       </c>
       <c r="K18" t="n">
-        <v>3.1387</v>
+        <v>3.6168</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8891</v>
+        <v>-0.0115</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.1624</v>
+        <v>-3.2864</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9707</v>
+        <v>-2.2415</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.1917</v>
+        <v>-1.0449</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5875</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.9377</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3502</v>
+        <v>2.7419</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7301</v>
+        <v>0.0573</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2506</v>
+        <v>0.127</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4796</v>
+        <v>-0.0697</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.7583</v>
+        <v>-2.3666</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.0576</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7007</v>
+        <v>-2.3666</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.4309</v>
+        <v>-3.0631</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8493</v>
+        <v>-1.6446</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5817</v>
+        <v>-1.4185</v>
       </c>
       <c r="G19" t="n">
         <v>-1.484</v>
@@ -1936,13 +1936,13 @@
         <v>0.9792</v>
       </c>
       <c r="S19" t="n">
-        <v>0.249</v>
+        <v>0.6168</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1494</v>
+        <v>0.0553</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3983</v>
+        <v>0.5615</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2166</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7384</v>
+        <v>-3.1631</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2107</v>
+        <v>-0.8014</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.5277</v>
+        <v>-2.3618</v>
       </c>
       <c r="G20" t="n">
         <v>-2.8828</v>
@@ -2014,13 +2014,13 @@
         <v>1.3709</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4212</v>
+        <v>0.1541</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3694</v>
+        <v>0.04</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0519</v>
+        <v>0.1141</v>
       </c>
       <c r="V20" t="n">
         <v>-0.8260999999999999</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-10.9793</v>
+        <v>-9.615199999999998</v>
       </c>
       <c r="E21" t="n">
         <v>3.9135</v>
       </c>
       <c r="F21" t="n">
-        <v>-14.893</v>
+        <v>-13.5286</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1402</v>
@@ -2062,7 +2062,7 @@
         <v>-6.4735</v>
       </c>
       <c r="I21" t="n">
-        <v>3.3332</v>
+        <v>3.333200000000001</v>
       </c>
       <c r="J21" t="n">
         <v>15.6718</v>
@@ -2092,13 +2092,13 @@
         <v>14.6885</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3968</v>
+        <v>-0.03220000000000003</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1295999999999999</v>
+        <v>-0.1294</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2674</v>
+        <v>0.09709999999999998</v>
       </c>
       <c r="V21" t="n">
         <v>-8.401</v>
